--- a/src/test/resources/auto-test-resources/maven-demo-mocked-resources.xlsx
+++ b/src/test/resources/auto-test-resources/maven-demo-mocked-resources.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="583">
   <si>
     <t>Class</t>
   </si>
@@ -199,7 +199,7 @@
 (J)Lorg/unlogged/demo/models/CustomerProfile;</t>
   </si>
   <si>
-    <t>{"customerid":0,"customername":"string","dateofbirth":"string","email":"string","contactnumber":"string","address":"string","referralcodes":["string"]}</t>
+    <t>{"customerid":0,"customername":"string","dateofbirth":"string","email":"string","contactnumber":"string","address":"string","referralcodes":["string"],"createdDate":"Jul 5, 2024 05:58:11 AM","updatedDate":"Jul 5, 2024 05:58:11 AM"}</t>
   </si>
   <si>
     <t>[{"id":"8c19c05c-6a14-48b5-b85f-0ecf53f7ae12","name":"mock response customerProfileRepository.fetchCustomerProfile","fieldTypeName":"org.unlogged.demo.repository.CustomerProfileRepository","sourceClassName":"org.unlogged.demo.service.CustomerService","fieldName":"customerProfileRepository","methodName":"fetchCustomerProfile","whenParameter":[{"name":"customerID","type":"ANY_OF_TYPE","value":"long"}],"thenParameter":[{"returnParameter":{"declaredMocks":[],"value":"{\"customerid\": \"0\", \"customername\": \"string\", \"dateofbirth\": \"string\", \"email\": \"string\", \"contactnumber\": \"string\", \"address\": \"string\", \"referralcodes\": [\"string\"]}","returnValueType":"REAL","className":"org.unlogged.demo.models.CustomerProfile"},"methodExitType":"NORMAL"}]}]</t>
@@ -236,7 +236,7 @@
 (J)Lorg/unlogged/demo/models/CustomerProfile;</t>
   </si>
   <si>
-    <t>{"customerid":0,"customername":"string","dateofbirth":"string","email":"string","contactnumber":"string","address":"string","referralcodes":["string","vxufxusjte"]}</t>
+    <t>{"customerid":0,"customername":"string","dateofbirth":"string","email":"string","contactnumber":"string","address":"string","referralcodes":["string","bidqhuulom"],"createdDate":"Jul 5, 2024 05:58:11 AM","updatedDate":"Jul 5, 2024 05:58:11 AM"}</t>
   </si>
   <si>
     <t>[{"id":"c59e6188-6544-4809-bc9f-c3163528aa5f","name":"mock response customerProfileRepository.fetchCustomerProfile","fieldTypeName":"org.unlogged.demo.repository.CustomerProfileRepository","sourceClassName":"org.unlogged.demo.service.CustomerService","fieldName":"customerProfileRepository","methodName":"fetchCustomerProfile","whenParameter":[{"name":"customerID","type":"ANY_OF_TYPE","value":"long"}],"thenParameter":[{"returnParameter":{"declaredMocks":[],"value":"{\"customerid\": \"0\", \"customername\": \"string\", \"dateofbirth\": \"string\", \"email\": \"string\", \"contactnumber\": \"string\", \"address\": \"string\", \"referralcodes\": [\"string\"]}","returnValueType":"REAL","className":"org.unlogged.demo.models.CustomerProfile"},"methodExitType":"NORMAL"}]},{"id":"80ff8087-e7b4-4296-8e41-0bd09042483b","name":"mock response customerProfileRepository.save","fieldTypeName":"org.unlogged.demo.repository.CustomerProfileRepository","sourceClassName":"org.unlogged.demo.service.CustomerService","fieldName":"customerProfileRepository","methodName":"save","whenParameter":[{"name":"profile","type":"ANY_OF_TYPE","value":"org.unlogged.demo.models.CustomerProfile"}],"thenParameter":[{"returnParameter":{"declaredMocks":[],"value":"{\"customerid\": \"0\", \"customername\": \"string\", \"dateofbirth\": \"string\", \"email\": \"string\", \"contactnumber\": \"string\", \"address\": \"string\", \"referralcodes\": [\"string\"]}","returnValueType":"REAL","className":"org.unlogged.demo.models.CustomerProfile"},"methodExitType":"NORMAL"}]}]</t>
@@ -284,7 +284,7 @@
 ()Ljava/util/concurrent/CompletableFuture;</t>
   </si>
   <si>
-    <t>{"done":true,"cancelled":false,"completedExceptionally":false,"numberOfDependents":0}</t>
+    <t>"yolo"</t>
   </si>
   <si>
     <t>java.util.concurrent.CompletableFuture&lt;java.lang.String&gt;</t>
@@ -624,7 +624,7 @@
 (Lorg/unlogged/demo/models/CustomerProfileRequest;)Lorg/unlogged/demo/models/CustomerProfile;</t>
   </si>
   <si>
-    <t>{"customerid":1,"customername":"string","dateofbirth":"string","email":"string","contactnumber":"string","address":"string","referralcodes":["string"]}</t>
+    <t>{"customerid":8,"customername":"string","dateofbirth":"string","email":"string","contactnumber":"string","address":"string","referralcodes":["string"],"createdDate":"Jul 5, 2024 05:58:16 AM","updatedDate":"Jul 5, 2024 05:58:16 AM"}</t>
   </si>
   <si>
     <t>save
@@ -1070,6 +1070,9 @@
   <si>
     <t>parser
 ()Lcom/google/protobuf/Parser;</t>
+  </si>
+  <si>
+    <t>{"className": "null"}</t>
   </si>
   <si>
     <t>com.google.protobuf.Parser&lt;org.unlogged.demo.protos.generated.Person&gt;</t>
@@ -2682,7 +2685,7 @@
       <c r="F11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -2740,7 +2743,7 @@
       <c r="F13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -2769,7 +2772,7 @@
       <c r="F14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -2798,7 +2801,7 @@
       <c r="F15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>67</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -2912,9 +2915,9 @@
         <v>17</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>81</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -4187,7 +4190,7 @@
       <c r="F63" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" s="2" t="s">
         <v>178</v>
       </c>
       <c r="J63" s="1" t="s">
@@ -5884,14 +5887,14 @@
       <c r="F118" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G118" s="1" t="s">
-        <v>163</v>
+      <c r="G118" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
@@ -5899,7 +5902,7 @@
         <v>197</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>197</v>
@@ -5913,14 +5916,14 @@
       <c r="F119" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G119" s="1" t="s">
-        <v>163</v>
+      <c r="G119" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="J119" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -5928,7 +5931,7 @@
         <v>197</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>197</v>
@@ -5989,7 +5992,7 @@
         <v>216</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>13</v>
@@ -6044,7 +6047,7 @@
         <v>218</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>31</v>
@@ -6056,10 +6059,10 @@
         <v>102</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>36</v>
@@ -6108,7 +6111,7 @@
         <v>219</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>31</v>
@@ -6120,10 +6123,10 @@
         <v>102</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>36</v>
@@ -6172,7 +6175,7 @@
         <v>222</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>13</v>
@@ -6230,7 +6233,7 @@
         <v>223</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>13</v>
@@ -6288,7 +6291,7 @@
         <v>224</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>13</v>
@@ -6343,7 +6346,7 @@
         <v>135</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>31</v>
@@ -6355,10 +6358,10 @@
         <v>102</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H134" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>36</v>
@@ -6407,7 +6410,7 @@
         <v>225</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>31</v>
@@ -6419,10 +6422,10 @@
         <v>102</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>36</v>
@@ -6471,7 +6474,7 @@
         <v>226</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>13</v>
@@ -6535,7 +6538,7 @@
         <v>232</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>31</v>
@@ -6547,10 +6550,10 @@
         <v>112</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>156</v>
@@ -6599,7 +6602,7 @@
         <v>230</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>13</v>
@@ -6657,7 +6660,7 @@
         <v>228</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>13</v>
@@ -6721,7 +6724,7 @@
         <v>236</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>31</v>
@@ -6733,10 +6736,10 @@
         <v>112</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>156</v>
@@ -6750,19 +6753,19 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B147" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="D147" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>15</v>
@@ -6779,19 +6782,19 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>15</v>
@@ -6808,13 +6811,13 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>31</v>
@@ -6826,7 +6829,7 @@
         <v>102</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>156</v>
@@ -6835,7 +6838,7 @@
         <v>17</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
@@ -6858,7 +6861,7 @@
         <v>15</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>17</v>
@@ -7012,7 +7015,7 @@
         <v>26</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K155" s="1" t="s">
         <v>27</v>
@@ -7038,10 +7041,10 @@
         <v>15</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K156" s="1" t="s">
         <v>197</v>
@@ -7067,16 +7070,16 @@
         <v>102</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K157" s="1" t="s">
         <v>204</v>
@@ -7134,7 +7137,7 @@
         <v>91</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K159" s="1" t="s">
         <v>131</v>
@@ -7163,7 +7166,7 @@
         <v>26</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K160" s="1" t="s">
         <v>27</v>
@@ -7218,7 +7221,7 @@
         <v>21</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>17</v>
@@ -7232,7 +7235,7 @@
         <v>193</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>193</v>
@@ -7247,16 +7250,16 @@
         <v>102</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K163" s="1" t="s">
         <v>193</v>
@@ -7267,7 +7270,7 @@
         <v>193</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>193</v>
@@ -7282,16 +7285,16 @@
         <v>102</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>193</v>
@@ -7302,7 +7305,7 @@
         <v>193</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>193</v>
@@ -7317,16 +7320,16 @@
         <v>112</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H165" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K165" s="1" t="s">
         <v>193</v>
@@ -7337,7 +7340,7 @@
         <v>193</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>193</v>
@@ -7352,16 +7355,16 @@
         <v>112</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K166" s="1" t="s">
         <v>193</v>
@@ -7372,7 +7375,7 @@
         <v>193</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>193</v>
@@ -7396,7 +7399,7 @@
         <v>36</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K167" s="1" t="s">
         <v>193</v>
@@ -7407,7 +7410,7 @@
         <v>193</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>193</v>
@@ -7431,7 +7434,7 @@
         <v>36</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K168" s="1" t="s">
         <v>193</v>
@@ -7442,7 +7445,7 @@
         <v>193</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>193</v>
@@ -7457,7 +7460,7 @@
         <v>15</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J169" s="1" t="s">
         <v>17</v>
@@ -7471,7 +7474,7 @@
         <v>193</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>193</v>
@@ -7486,7 +7489,7 @@
         <v>15</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J170" s="1" t="s">
         <v>17</v>
@@ -7500,7 +7503,7 @@
         <v>193</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>193</v>
@@ -7515,10 +7518,10 @@
         <v>112</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>36</v>
@@ -7535,7 +7538,7 @@
         <v>193</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>193</v>
@@ -7550,10 +7553,10 @@
         <v>112</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>36</v>
@@ -7570,7 +7573,7 @@
         <v>193</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>193</v>
@@ -7585,10 +7588,10 @@
         <v>102</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>36</v>
@@ -7605,7 +7608,7 @@
         <v>193</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>193</v>
@@ -7620,10 +7623,10 @@
         <v>102</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>36</v>
@@ -7640,7 +7643,7 @@
         <v>193</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>193</v>
@@ -7655,13 +7658,13 @@
         <v>15</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J175" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
@@ -7669,7 +7672,7 @@
         <v>193</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>193</v>
@@ -7684,13 +7687,13 @@
         <v>15</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -7698,7 +7701,7 @@
         <v>193</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>193</v>
@@ -7707,19 +7710,19 @@
         <v>13</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
@@ -7727,7 +7730,7 @@
         <v>193</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>193</v>
@@ -7742,13 +7745,13 @@
         <v>15</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J178" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K178" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -7756,7 +7759,7 @@
         <v>193</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>193</v>
@@ -7771,13 +7774,13 @@
         <v>21</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J179" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K179" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -7785,7 +7788,7 @@
         <v>193</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>193</v>
@@ -7800,7 +7803,7 @@
         <v>21</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J180" s="1" t="s">
         <v>17</v>
@@ -7828,14 +7831,14 @@
       <c r="F181" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G181" s="1" t="s">
-        <v>163</v>
+      <c r="G181" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="J181" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K181" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -7843,7 +7846,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>193</v>
@@ -7857,14 +7860,14 @@
       <c r="F182" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G182" s="1" t="s">
-        <v>163</v>
+      <c r="G182" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="J182" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
@@ -7872,7 +7875,7 @@
         <v>193</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>193</v>
@@ -7887,7 +7890,7 @@
         <v>21</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J183" s="1" t="s">
         <v>17</v>
@@ -7898,13 +7901,13 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B184" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="D184" s="1" t="s">
         <v>13</v>
@@ -7924,13 +7927,13 @@
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>13</v>
@@ -7953,13 +7956,13 @@
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>13</v>
@@ -7979,13 +7982,13 @@
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>13</v>
@@ -8008,13 +8011,13 @@
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>13</v>
@@ -8037,13 +8040,13 @@
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D189" s="1" t="s">
         <v>13</v>
@@ -8066,13 +8069,13 @@
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>13</v>
@@ -8084,7 +8087,7 @@
         <v>102</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>17</v>
@@ -8095,13 +8098,13 @@
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B191" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C191" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>13</v>
@@ -8119,24 +8122,24 @@
         <v>17</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F192" s="2" t="s">
         <v>102</v>
@@ -8153,13 +8156,13 @@
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>13</v>
@@ -8177,24 +8180,24 @@
         <v>17</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F194" s="2" t="s">
         <v>102</v>
@@ -8211,13 +8214,13 @@
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>13</v>
@@ -8240,13 +8243,13 @@
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>13</v>
@@ -8269,13 +8272,13 @@
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>13</v>
@@ -8287,30 +8290,30 @@
         <v>102</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J197" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>102</v>
@@ -8327,13 +8330,13 @@
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>13</v>
@@ -8351,24 +8354,24 @@
         <v>17</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>102</v>
@@ -8385,13 +8388,13 @@
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>13</v>
@@ -8409,24 +8412,24 @@
         <v>17</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>102</v>
@@ -8443,13 +8446,13 @@
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>13</v>
@@ -8472,13 +8475,13 @@
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>13</v>
@@ -8501,13 +8504,13 @@
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>13</v>
@@ -8527,13 +8530,13 @@
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>13</v>
@@ -8556,13 +8559,13 @@
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>13</v>
@@ -8580,24 +8583,24 @@
         <v>17</v>
       </c>
       <c r="K207" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>102</v>
@@ -8614,13 +8617,13 @@
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>13</v>
@@ -8638,24 +8641,24 @@
         <v>17</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>102</v>
@@ -8672,13 +8675,13 @@
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>13</v>
@@ -8696,24 +8699,24 @@
         <v>17</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>102</v>
@@ -8730,13 +8733,13 @@
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>13</v>
@@ -8754,24 +8757,24 @@
         <v>17</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>102</v>
@@ -8788,13 +8791,13 @@
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>13</v>
@@ -8817,13 +8820,13 @@
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>13</v>
@@ -8846,13 +8849,13 @@
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>13</v>
@@ -8875,13 +8878,13 @@
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>13</v>
@@ -8904,13 +8907,13 @@
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>13</v>
@@ -8928,24 +8931,24 @@
         <v>17</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F220" s="2" t="s">
         <v>102</v>
@@ -8962,13 +8965,13 @@
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>13</v>
@@ -8986,24 +8989,24 @@
         <v>17</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>102</v>
@@ -9020,13 +9023,13 @@
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>13</v>
@@ -9044,24 +9047,24 @@
         <v>17</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>102</v>
@@ -9078,13 +9081,13 @@
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D225" s="1" t="s">
         <v>13</v>
@@ -9102,24 +9105,24 @@
         <v>17</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>102</v>
@@ -9136,13 +9139,13 @@
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D227" s="1" t="s">
         <v>13</v>
@@ -9160,24 +9163,24 @@
         <v>17</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>102</v>
@@ -9194,13 +9197,13 @@
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D229" s="1" t="s">
         <v>13</v>
@@ -9218,24 +9221,24 @@
         <v>17</v>
       </c>
       <c r="K229" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>102</v>
@@ -9252,13 +9255,13 @@
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D231" s="1" t="s">
         <v>13</v>
@@ -9276,24 +9279,24 @@
         <v>17</v>
       </c>
       <c r="K231" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D232" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F232" s="2" t="s">
         <v>102</v>
@@ -9310,13 +9313,13 @@
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>13</v>
@@ -9328,7 +9331,7 @@
         <v>102</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>17</v>
@@ -9339,13 +9342,13 @@
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>218</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D234" s="1" t="s">
         <v>13</v>
@@ -9365,13 +9368,13 @@
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B235" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C235" s="1" t="s">
         <v>432</v>
-      </c>
-      <c r="C235" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>13</v>
@@ -9394,13 +9397,13 @@
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D236" s="1" t="s">
         <v>13</v>
@@ -9420,13 +9423,13 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>13</v>
@@ -9449,13 +9452,13 @@
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D238" s="1" t="s">
         <v>13</v>
@@ -9475,13 +9478,13 @@
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>13</v>
@@ -9504,13 +9507,13 @@
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>13</v>
@@ -9528,24 +9531,24 @@
         <v>17</v>
       </c>
       <c r="K240" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F241" s="2" t="s">
         <v>102</v>
@@ -9562,13 +9565,13 @@
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>13</v>
@@ -9586,24 +9589,24 @@
         <v>17</v>
       </c>
       <c r="K242" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F243" s="2" t="s">
         <v>102</v>
@@ -9620,13 +9623,13 @@
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>13</v>
@@ -9646,13 +9649,13 @@
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>13</v>
@@ -9675,13 +9678,13 @@
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>13</v>
@@ -9704,13 +9707,13 @@
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>13</v>
@@ -9733,13 +9736,13 @@
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>13</v>
@@ -9759,13 +9762,13 @@
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>13</v>
@@ -9788,13 +9791,13 @@
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>13</v>
@@ -9806,7 +9809,7 @@
         <v>102</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J250" s="1" t="s">
         <v>17</v>
@@ -9820,7 +9823,7 @@
         <v>89</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>89</v>
@@ -9835,7 +9838,7 @@
         <v>102</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>17</v>
@@ -9849,7 +9852,7 @@
         <v>89</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>89</v>
@@ -9864,13 +9867,13 @@
         <v>102</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="253" ht="15.75" customHeight="1">
@@ -9878,7 +9881,7 @@
         <v>89</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>89</v>
@@ -9887,7 +9890,7 @@
         <v>13</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>102</v>
@@ -9907,7 +9910,7 @@
         <v>89</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>89</v>
@@ -9922,13 +9925,13 @@
         <v>102</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>17</v>
       </c>
       <c r="K254" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
@@ -9936,7 +9939,7 @@
         <v>89</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>89</v>
@@ -9945,7 +9948,7 @@
         <v>13</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F255" s="2" t="s">
         <v>102</v>
@@ -9962,13 +9965,13 @@
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B256" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C256" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>457</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>13</v>
@@ -9991,19 +9994,19 @@
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>102</v>
@@ -10020,13 +10023,13 @@
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>13</v>
@@ -10038,7 +10041,7 @@
         <v>102</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>17</v>
@@ -10049,13 +10052,13 @@
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>13</v>
@@ -10078,13 +10081,13 @@
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>13</v>
@@ -10096,7 +10099,7 @@
         <v>102</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J260" s="1" t="s">
         <v>17</v>
@@ -10107,13 +10110,13 @@
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B261" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C261" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="C261" s="1" t="s">
-        <v>465</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>13</v>
@@ -10133,13 +10136,13 @@
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>13</v>
@@ -10162,13 +10165,13 @@
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>13</v>
@@ -10188,13 +10191,13 @@
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>13</v>
@@ -10217,13 +10220,13 @@
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>13</v>
@@ -10243,13 +10246,13 @@
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>136</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>13</v>
@@ -10272,13 +10275,13 @@
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>13</v>
@@ -10298,13 +10301,13 @@
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>13</v>
@@ -10327,13 +10330,13 @@
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>13</v>
@@ -10353,13 +10356,13 @@
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>13</v>
@@ -10382,13 +10385,13 @@
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>13</v>
@@ -10411,19 +10414,19 @@
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F272" s="2" t="s">
         <v>102</v>
@@ -10443,7 +10446,7 @@
         <v>61</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>61</v>
@@ -10458,7 +10461,7 @@
         <v>102</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>17</v>
@@ -10472,7 +10475,7 @@
         <v>61</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>61</v>
@@ -10501,7 +10504,7 @@
         <v>61</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>61</v>
@@ -10530,7 +10533,7 @@
         <v>61</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>61</v>
@@ -10559,7 +10562,7 @@
         <v>61</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>61</v>
@@ -10588,7 +10591,7 @@
         <v>61</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>61</v>
@@ -10597,7 +10600,7 @@
         <v>13</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F278" s="2" t="s">
         <v>102</v>
@@ -10614,13 +10617,13 @@
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B279" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C279" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="C279" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>13</v>
@@ -10638,18 +10641,18 @@
         <v>17</v>
       </c>
       <c r="K279" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>13</v>
@@ -10672,13 +10675,13 @@
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>13</v>
@@ -10698,13 +10701,13 @@
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>13</v>
@@ -10727,13 +10730,13 @@
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>13</v>
@@ -10753,19 +10756,19 @@
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>102</v>
@@ -10782,13 +10785,13 @@
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>13</v>
@@ -10806,18 +10809,18 @@
         <v>17</v>
       </c>
       <c r="K285" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>13</v>
@@ -10840,13 +10843,13 @@
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>13</v>
@@ -10858,7 +10861,7 @@
         <v>102</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>17</v>
@@ -10872,7 +10875,7 @@
         <v>53</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>53</v>
@@ -10893,7 +10896,7 @@
         <v>17</v>
       </c>
       <c r="K288" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="289" ht="15.75" customHeight="1">
@@ -10901,7 +10904,7 @@
         <v>53</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>53</v>
@@ -10930,7 +10933,7 @@
         <v>53</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>53</v>
@@ -10956,7 +10959,7 @@
         <v>53</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>53</v>
@@ -10985,7 +10988,7 @@
         <v>53</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>53</v>
@@ -11011,7 +11014,7 @@
         <v>53</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>53</v>
@@ -11095,7 +11098,7 @@
         <v>53</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>53</v>
@@ -11121,7 +11124,7 @@
         <v>53</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>53</v>
@@ -11150,7 +11153,7 @@
         <v>53</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>53</v>
@@ -11176,7 +11179,7 @@
         <v>53</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>53</v>
@@ -11205,7 +11208,7 @@
         <v>53</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>53</v>
@@ -11234,7 +11237,7 @@
         <v>53</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>53</v>
@@ -11243,7 +11246,7 @@
         <v>13</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>102</v>
@@ -11263,7 +11266,7 @@
         <v>53</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>53</v>
@@ -11278,7 +11281,7 @@
         <v>102</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J302" s="1" t="s">
         <v>17</v>
@@ -11292,7 +11295,7 @@
         <v>42</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>42</v>
@@ -11307,7 +11310,7 @@
         <v>102</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>17</v>
@@ -11321,7 +11324,7 @@
         <v>42</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>42</v>
@@ -11350,7 +11353,7 @@
         <v>42</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>42</v>
@@ -11379,7 +11382,7 @@
         <v>42</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>42</v>
@@ -11388,7 +11391,7 @@
         <v>13</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F306" s="2" t="s">
         <v>102</v>
@@ -11408,7 +11411,7 @@
         <v>42</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>42</v>
@@ -11437,7 +11440,7 @@
         <v>42</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>42</v>
@@ -11446,7 +11449,7 @@
         <v>13</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F308" s="2" t="s">
         <v>102</v>
@@ -11466,7 +11469,7 @@
         <v>42</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>42</v>
@@ -11481,7 +11484,7 @@
         <v>102</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>17</v>
@@ -11495,7 +11498,7 @@
         <v>42</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>42</v>
@@ -11504,7 +11507,7 @@
         <v>13</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F310" s="2" t="s">
         <v>102</v>
@@ -11521,13 +11524,13 @@
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B311" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="C311" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>509</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>13</v>
@@ -11539,10 +11542,10 @@
         <v>21</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J311" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K311" s="1" t="s">
         <v>53</v>
@@ -11550,13 +11553,13 @@
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>13</v>
@@ -11568,10 +11571,10 @@
         <v>21</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J312" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K312" s="1" t="s">
         <v>53</v>
@@ -11579,13 +11582,13 @@
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>13</v>
@@ -11597,10 +11600,10 @@
         <v>21</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J313" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K313" s="1" t="s">
         <v>53</v>
@@ -11608,13 +11611,13 @@
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>13</v>
@@ -11626,10 +11629,10 @@
         <v>21</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J314" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K314" s="1" t="s">
         <v>53</v>
@@ -11637,13 +11640,13 @@
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>13</v>
@@ -11655,10 +11658,10 @@
         <v>21</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="J315" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K315" s="1" t="s">
         <v>61</v>
@@ -11666,13 +11669,13 @@
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B316" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C316" s="1" t="s">
         <v>523</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>522</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>13</v>
@@ -11684,7 +11687,7 @@
         <v>15</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>17</v>
@@ -11695,13 +11698,13 @@
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>31</v>
@@ -11713,7 +11716,7 @@
         <v>102</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>156</v>
@@ -11722,18 +11725,18 @@
         <v>17</v>
       </c>
       <c r="K317" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>13</v>
@@ -11745,7 +11748,7 @@
         <v>15</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>17</v>
@@ -11756,28 +11759,28 @@
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F319" s="2" t="s">
         <v>102</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>36</v>
@@ -11791,13 +11794,13 @@
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B320" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C320" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>31</v>
@@ -11812,7 +11815,7 @@
         <v>16</v>
       </c>
       <c r="J320" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="K320" s="1" t="s">
         <v>18</v>
@@ -11820,13 +11823,13 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>13</v>
@@ -11841,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="J321" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="K321" s="1" t="s">
         <v>18</v>
@@ -11849,13 +11852,13 @@
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B322" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="C322" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>13</v>
@@ -11870,7 +11873,7 @@
         <v>91</v>
       </c>
       <c r="J322" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="K322" s="1" t="s">
         <v>131</v>
@@ -11878,13 +11881,13 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B323" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C323" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="C323" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="D323" s="3" t="s">
         <v>13</v>
@@ -11896,16 +11899,16 @@
         <v>15</v>
       </c>
       <c r="G323" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H323" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I323" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K323" s="3"/>
       <c r="L323" s="3"/>
@@ -11922,34 +11925,34 @@
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D324" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G324" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H324" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I324" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K324" s="3"/>
       <c r="L324" s="3"/>
@@ -11966,13 +11969,13 @@
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D325" s="3" t="s">
         <v>13</v>
@@ -11984,16 +11987,16 @@
         <v>15</v>
       </c>
       <c r="G325" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H325" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I325" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K325" s="3"/>
       <c r="L325" s="3"/>
@@ -12010,34 +12013,34 @@
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D326" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G326" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H326" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I326" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K326" s="3"/>
       <c r="L326" s="3"/>
@@ -12054,13 +12057,13 @@
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>13</v>
@@ -12075,13 +12078,13 @@
         <v>91</v>
       </c>
       <c r="H327" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I327" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K327" s="3"/>
       <c r="L327" s="3"/>
@@ -12098,13 +12101,13 @@
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B328" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C328" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C328" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>13</v>
@@ -12116,16 +12119,16 @@
         <v>21</v>
       </c>
       <c r="G328" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H328" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I328" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="K328" s="3"/>
       <c r="L328" s="3"/>
@@ -12142,34 +12145,34 @@
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B329" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C329" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="C329" s="3" t="s">
-        <v>562</v>
-      </c>
       <c r="D329" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G329" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H329" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I329" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K329" s="3"/>
       <c r="L329" s="3"/>
@@ -12186,13 +12189,13 @@
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>13</v>
@@ -12207,13 +12210,13 @@
         <v>91</v>
       </c>
       <c r="H330" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I330" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K330" s="3"/>
       <c r="L330" s="3"/>
@@ -12230,13 +12233,13 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D331" s="3" t="s">
         <v>13</v>
@@ -12248,13 +12251,13 @@
         <v>15</v>
       </c>
       <c r="G331" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H331" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I331" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J331" s="3" t="s">
         <v>17</v>
@@ -12274,31 +12277,31 @@
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B332" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G332" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H332" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I332" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J332" s="3" t="s">
         <v>17</v>
@@ -12318,31 +12321,31 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G333" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I333" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J333" s="3" t="s">
         <v>17</v>
@@ -12362,34 +12365,34 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G334" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H334" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I334" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K334" s="3"/>
       <c r="L334" s="3"/>
@@ -12406,13 +12409,13 @@
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>13</v>
@@ -12424,16 +12427,16 @@
         <v>15</v>
       </c>
       <c r="G335" s="6" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H335" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I335" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="J335" s="6" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K335" s="3"/>
       <c r="L335" s="3"/>
